--- a/survey_templates/039_cost_allocation_efficiency_survey--survey_templates.xlsx
+++ b/survey_templates/039_cost_allocation_efficiency_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>cost_allocation_efficiency_survey</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cost_allocation_efficiency_survey</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>current_processes</t>
+          <t>What are the current cost processes used in your department?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>transparency</t>
+          <t>challenges</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>transparency</t>
+          <t>What are the main challenges faced in the current cost processes?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>cost_center</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>Which cost center should be allocated the highest priority?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>cost_allocation_process</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>What is the current cost allocation process used in your department?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_page_2</t>
+          <t>cost_center_performance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cost_center</t>
+          <t>What is the current cost center performance?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>first_page_2</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cost_center</t>
+          <t>Do you have any additional comments or suggestions for improving cost allocation efficiency?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>first_page_2</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cost_center_1</t>
+          <t>Do you have any notes on the cost allocation process?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,389 +699,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>first_page_2</t>
+          <t>transparency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cost_center_2</t>
+          <t>How transparent is the current cost allocation process?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>first_page_2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>cost_center_3</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>cost_allocation_process</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>cost_allocation_process</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>cost_allocation_process</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>cost_allocation_process</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>transparency</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>cost_allocation_process</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>cost_center_1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>transparency</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>cost_center_1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1228,646 +860,153 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>first_page_2_choices</t>
+          <t>cost_center_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'cost_center_1',_'value':_1}</t>
+          <t>cost_center_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'cost_center_1', 'value': 1}</t>
+          <t>cost center 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>first_page_2_choices</t>
+          <t>cost_center_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'cost_center_2',_'value':_2}</t>
+          <t>cost_center_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'cost_center_2', 'value': 2}</t>
+          <t>cost center 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>first_page_2_choices</t>
+          <t>cost_center_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'cost_center_3',_'value':_3}</t>
+          <t>cost_center_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'cost_center_3', 'value': 3}</t>
+          <t>cost center 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>first_page_2_choices</t>
+          <t>cost_allocation_process_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'cost_center_1',_'value':_1}</t>
+          <t>process1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'cost_center_1', 'value': 1}</t>
+          <t>process1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>first_page_2_choices</t>
+          <t>cost_allocation_process_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'cost_center_2',_'value':_2}</t>
+          <t>process2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'cost_center_2', 'value': 2}</t>
+          <t>process2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>first_page_2_choices</t>
+          <t>cost_allocation_process_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'cost_center_3',_'value':_3}</t>
+          <t>process3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'cost_center_3', 'value': 3}</t>
+          <t>process3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>second_page_choices</t>
+          <t>transparency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>process1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>process1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>second_page_choices</t>
+          <t>transparency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>process2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>process2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>second_page_choices</t>
+          <t>transparency_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>process3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>process3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>process1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>process1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>process2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>process2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>process3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>process3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>process1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>process1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>process2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>process2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>process3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>process3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>process1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>process1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>process2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>process2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>process3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>process3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>process1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>process1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>process2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>process2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>process3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>process3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'label':_'cost_center_1',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'label': 'cost_center_1', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'label':_'cost_center_2',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'label': 'cost_center_2', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'label':_'cost_center_3',_'value':_3}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'label': 'cost_center_3', 'value': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'label':_'cost_center_1',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'label': 'cost_center_1', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'label':_'cost_center_2',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'label': 'cost_center_2', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'label':_'cost_center_3',_'value':_3}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'label': 'cost_center_3', 'value': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'label':_'option1',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'label': 'option1', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'label':_'option2',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'label': 'option2', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'label':_'option3',_'value':_3}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'label': 'option3', 'value': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'label':_'cost_center_1',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'label': 'cost_center_1', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'label':_'cost_center_2',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'label': 'cost_center_2', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'label':_'cost_center_3',_'value':_3}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'label': 'cost_center_3', 'value': 3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>second_page_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
